--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260811.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -682,29 +682,29 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>47,068,000</t>
+          <t>4,413,802,069</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -726,29 +726,29 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>47,068,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -770,29 +770,29 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -814,29 +814,29 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3,891,938,651</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>11,165,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,165,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>2,169,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,169,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1166,183 +1166,183 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,535,985,322</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>2,547,385,322</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1364,68 +1364,68 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,66 +1437,66 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1540,73 +1540,73 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-4,487,572</t>
+          <t>-27,532,786</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
